--- a/data/clients.xlsx
+++ b/data/clients.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="20">
   <si>
     <t>Client Name</t>
   </si>
@@ -46,16 +46,25 @@
     <t>Ramesh</t>
   </si>
   <si>
+    <t>Rahul</t>
+  </si>
+  <si>
     <t>bhrpl6522e</t>
   </si>
   <si>
     <t>bhrpl6522d</t>
   </si>
   <si>
+    <t>jdnkn3737r</t>
+  </si>
+  <si>
     <t>36DCRPS5473P1ZC</t>
   </si>
   <si>
     <t>36DCRPS5473P1Ze</t>
+  </si>
+  <si>
+    <t>36kshdh2737nd24</t>
   </si>
   <si>
     <t>2026-27</t>
@@ -396,7 +405,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -430,25 +439,25 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -456,25 +465,51 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" t="s">
         <v>13</v>
       </c>
-      <c r="D3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" t="s">
-        <v>15</v>
-      </c>
-      <c r="H3" t="s">
+      <c r="C4" t="s">
         <v>16</v>
+      </c>
+      <c r="D4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H4" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/data/clients.xlsx
+++ b/data/clients.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="23">
   <si>
     <t>Client Name</t>
   </si>
@@ -49,6 +49,9 @@
     <t>Rahul</t>
   </si>
   <si>
+    <t>Raju</t>
+  </si>
+  <si>
     <t>bhrpl6522e</t>
   </si>
   <si>
@@ -58,6 +61,9 @@
     <t>jdnkn3737r</t>
   </si>
   <si>
+    <t>hshsh2727y</t>
+  </si>
+  <si>
     <t>36DCRPS5473P1ZC</t>
   </si>
   <si>
@@ -65,6 +71,9 @@
   </si>
   <si>
     <t>36kshdh2737nd24</t>
+  </si>
+  <si>
+    <t>sdvbksdjvskjvn</t>
   </si>
   <si>
     <t>2026-27</t>
@@ -405,7 +414,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -439,25 +448,25 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -465,25 +474,25 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D3" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E3" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F3" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G3" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H3" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -491,25 +500,51 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D4" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E4" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F4" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G4" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" t="s">
         <v>19</v>
+      </c>
+      <c r="D5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" t="s">
+        <v>21</v>
+      </c>
+      <c r="G5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H5" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/data/clients.xlsx
+++ b/data/clients.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="27">
   <si>
     <t>Client Name</t>
   </si>
@@ -40,6 +40,9 @@
     <t>Assigned Staff</t>
   </si>
   <si>
+    <t>Checklist Completion %</t>
+  </si>
+  <si>
     <t>Abhishek</t>
   </si>
   <si>
@@ -52,6 +55,9 @@
     <t>Raju</t>
   </si>
   <si>
+    <t>lokesh</t>
+  </si>
+  <si>
     <t>bhrpl6522e</t>
   </si>
   <si>
@@ -64,6 +70,9 @@
     <t>hshsh2727y</t>
   </si>
   <si>
+    <t>hshsh2727h</t>
+  </si>
+  <si>
     <t>36DCRPS5473P1ZC</t>
   </si>
   <si>
@@ -74,6 +83,9 @@
   </si>
   <si>
     <t>sdvbksdjvskjvn</t>
+  </si>
+  <si>
+    <t>bchdvbsdvbk</t>
   </si>
   <si>
     <t>2026-27</t>
@@ -414,10 +426,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -442,109 +454,141 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" t="s">
         <v>12</v>
       </c>
-      <c r="C2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H2" t="s">
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" t="s">
         <v>22</v>
       </c>
+      <c r="D5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H5" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="3" spans="1:8">
-      <c r="A3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" t="s">
+    <row r="6" spans="1:9">
+      <c r="A6" t="s">
         <v>13</v>
       </c>
-      <c r="C3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="B6" t="s">
         <v>18</v>
       </c>
-      <c r="D4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4" t="s">
-        <v>21</v>
-      </c>
-      <c r="G4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E5" t="s">
-        <v>21</v>
-      </c>
-      <c r="F5" t="s">
-        <v>21</v>
-      </c>
-      <c r="G5" t="s">
-        <v>21</v>
-      </c>
-      <c r="H5" t="s">
-        <v>22</v>
+      <c r="C6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" t="s">
+        <v>25</v>
+      </c>
+      <c r="G6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H6" t="s">
+        <v>26</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data/clients.xlsx
+++ b/data/clients.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="30">
   <si>
     <t>Client Name</t>
   </si>
@@ -28,13 +28,16 @@
     <t>AY</t>
   </si>
   <si>
+    <t>Document Status</t>
+  </si>
+  <si>
     <t>Audit Status</t>
   </si>
   <si>
-    <t>Docs Status</t>
-  </si>
-  <si>
-    <t>Filing Status</t>
+    <t>3CD/3CA Filing Status</t>
+  </si>
+  <si>
+    <t>ITR Filing Status</t>
   </si>
   <si>
     <t>Assigned Staff</t>
@@ -92,6 +95,12 @@
   </si>
   <si>
     <t>Pending</t>
+  </si>
+  <si>
+    <t>Received</t>
+  </si>
+  <si>
+    <t>Not Filed</t>
   </si>
   <si>
     <t>Lokesh</t>
@@ -426,10 +435,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -457,137 +466,167 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I3" t="s">
+        <v>29</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I4" t="s">
+        <v>29</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5" t="s">
+        <v>26</v>
+      </c>
+      <c r="G5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5" t="s">
+        <v>28</v>
+      </c>
+      <c r="I5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" t="s">
         <v>14</v>
       </c>
-      <c r="C2" t="s">
+      <c r="B6" t="s">
         <v>19</v>
       </c>
-      <c r="D2" t="s">
+      <c r="C6" t="s">
         <v>24</v>
       </c>
-      <c r="E2" t="s">
+      <c r="D6" t="s">
         <v>25</v>
       </c>
-      <c r="F2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
-      <c r="A3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
-      <c r="A4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E4" t="s">
-        <v>25</v>
-      </c>
-      <c r="F4" t="s">
-        <v>25</v>
-      </c>
-      <c r="G4" t="s">
-        <v>25</v>
-      </c>
-      <c r="H4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="A5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F5" t="s">
-        <v>25</v>
-      </c>
-      <c r="G5" t="s">
-        <v>25</v>
-      </c>
-      <c r="H5" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="A6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" t="s">
-        <v>23</v>
-      </c>
-      <c r="D6" t="s">
-        <v>24</v>
-      </c>
       <c r="E6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G6" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="H6" t="s">
-        <v>26</v>
-      </c>
-      <c r="I6">
+        <v>28</v>
+      </c>
+      <c r="I6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J6">
         <v>0</v>
       </c>
     </row>

--- a/data/clients.xlsx
+++ b/data/clients.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="33">
   <si>
     <t>Client Name</t>
   </si>
@@ -61,6 +61,9 @@
     <t>lokesh</t>
   </si>
   <si>
+    <t>Poojamani</t>
+  </si>
+  <si>
     <t>bhrpl6522e</t>
   </si>
   <si>
@@ -76,6 +79,9 @@
     <t>hshsh2727h</t>
   </si>
   <si>
+    <t>hshsh5252f</t>
+  </si>
+  <si>
     <t>36DCRPS5473P1ZC</t>
   </si>
   <si>
@@ -89,6 +95,9 @@
   </si>
   <si>
     <t>bchdvbsdvbk</t>
+  </si>
+  <si>
+    <t>hbdbvdhvbksdvk</t>
   </si>
   <si>
     <t>2026-27</t>
@@ -435,7 +444,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
@@ -475,28 +484,28 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="H2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="I2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -507,28 +516,28 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="H3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="I3" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -539,28 +548,28 @@
         <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C4" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="H4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="I4" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -571,28 +580,28 @@
         <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D5" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E5" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G5" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="H5" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="I5" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="J5">
         <v>100</v>
@@ -603,30 +612,62 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C6" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D6" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E6" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F6" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H6" t="s">
+        <v>31</v>
+      </c>
+      <c r="I6" t="s">
+        <v>32</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" t="s">
         <v>28</v>
       </c>
-      <c r="H6" t="s">
-        <v>28</v>
-      </c>
-      <c r="I6" t="s">
-        <v>29</v>
-      </c>
-      <c r="J6">
+      <c r="E7" t="s">
+        <v>29</v>
+      </c>
+      <c r="F7" t="s">
+        <v>29</v>
+      </c>
+      <c r="G7" t="s">
+        <v>31</v>
+      </c>
+      <c r="H7" t="s">
+        <v>31</v>
+      </c>
+      <c r="I7" t="s">
+        <v>14</v>
+      </c>
+      <c r="J7">
         <v>0</v>
       </c>
     </row>

--- a/data/clients.xlsx
+++ b/data/clients.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="35">
   <si>
     <t>Client Name</t>
   </si>
@@ -109,7 +109,13 @@
     <t>Received</t>
   </si>
   <si>
+    <t>Completed</t>
+  </si>
+  <si>
     <t>Not Filed</t>
+  </si>
+  <si>
+    <t>Filed</t>
   </si>
   <si>
     <t>Lokesh</t>
@@ -499,13 +505,13 @@
         <v>29</v>
       </c>
       <c r="G2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -531,13 +537,13 @@
         <v>29</v>
       </c>
       <c r="G3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -563,13 +569,13 @@
         <v>29</v>
       </c>
       <c r="G4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -595,13 +601,13 @@
         <v>29</v>
       </c>
       <c r="G5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J5">
         <v>100</v>
@@ -627,13 +633,13 @@
         <v>29</v>
       </c>
       <c r="G6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -653,22 +659,22 @@
         <v>28</v>
       </c>
       <c r="E7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G7" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H7" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I7" t="s">
         <v>14</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/data/clients.xlsx
+++ b/data/clients.xlsx
@@ -64,7 +64,7 @@
     <t>Poojamani</t>
   </si>
   <si>
-    <t>bhrpl6522e</t>
+    <t>BHRPL6522E</t>
   </si>
   <si>
     <t>bhrpl6522d</t>

--- a/data/clients.xlsx
+++ b/data/clients.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="38">
   <si>
     <t>Client Name</t>
   </si>
@@ -64,6 +64,9 @@
     <t>Poojamani</t>
   </si>
   <si>
+    <t>mahesh</t>
+  </si>
+  <si>
     <t>BHRPL6522E</t>
   </si>
   <si>
@@ -82,6 +85,9 @@
     <t>hshsh5252f</t>
   </si>
   <si>
+    <t>BHYEJ2828E</t>
+  </si>
+  <si>
     <t>36DCRPS5473P1ZC</t>
   </si>
   <si>
@@ -98,6 +104,9 @@
   </si>
   <si>
     <t>hbdbvdhvbksdvk</t>
+  </si>
+  <si>
+    <t>KDVSIYDVBSDNYI</t>
   </si>
   <si>
     <t>2026-27</t>
@@ -450,7 +459,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
@@ -490,28 +499,28 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G2" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="H2" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="I2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -522,28 +531,28 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E3" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F3" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G3" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="H3" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="I3" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -554,28 +563,28 @@
         <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E4" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F4" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="H4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="I4" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -586,28 +595,28 @@
         <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D5" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F5" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G5" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="H5" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="I5" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="J5">
         <v>100</v>
@@ -618,28 +627,28 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C6" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D6" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E6" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F6" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G6" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="H6" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="I6" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -650,31 +659,63 @@
         <v>15</v>
       </c>
       <c r="B7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C7" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D7" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E7" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F7" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G7" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="H7" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I7" t="s">
         <v>14</v>
       </c>
       <c r="J7">
         <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>31</v>
+      </c>
+      <c r="E8" t="s">
+        <v>32</v>
+      </c>
+      <c r="F8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G8" t="s">
+        <v>35</v>
+      </c>
+      <c r="H8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I8" t="s">
+        <v>14</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data/clients.xlsx
+++ b/data/clients.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="40">
   <si>
     <t>Client Name</t>
   </si>
@@ -67,6 +67,9 @@
     <t>mahesh</t>
   </si>
   <si>
+    <t>Ramya</t>
+  </si>
+  <si>
     <t>BHRPL6522E</t>
   </si>
   <si>
@@ -86,6 +89,9 @@
   </si>
   <si>
     <t>BHYEJ2828E</t>
+  </si>
+  <si>
+    <t>HSHSH3535G</t>
   </si>
   <si>
     <t>36DCRPS5473P1ZC</t>
@@ -459,7 +465,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
@@ -499,28 +505,28 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -531,28 +537,28 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -563,28 +569,28 @@
         <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D4" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -595,28 +601,28 @@
         <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E5" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G5" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H5" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="J5">
         <v>100</v>
@@ -627,28 +633,28 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D6" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -659,25 +665,25 @@
         <v>15</v>
       </c>
       <c r="B7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D7" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E7" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G7" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H7" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="I7" t="s">
         <v>14</v>
@@ -691,30 +697,56 @@
         <v>16</v>
       </c>
       <c r="B8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C8" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D8" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G8" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H8" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I8" t="s">
         <v>14</v>
       </c>
       <c r="J8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" t="s">
+        <v>33</v>
+      </c>
+      <c r="E9" t="s">
+        <v>34</v>
+      </c>
+      <c r="F9" t="s">
+        <v>34</v>
+      </c>
+      <c r="G9" t="s">
+        <v>37</v>
+      </c>
+      <c r="H9" t="s">
+        <v>37</v>
+      </c>
+      <c r="J9">
         <v>0</v>
       </c>
     </row>

--- a/data/clients.xlsx
+++ b/data/clients.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>Client Name</t>
   </si>
@@ -44,96 +44,6 @@
   </si>
   <si>
     <t>Checklist Completion %</t>
-  </si>
-  <si>
-    <t>Abhishek</t>
-  </si>
-  <si>
-    <t>Ramesh</t>
-  </si>
-  <si>
-    <t>Rahul</t>
-  </si>
-  <si>
-    <t>Raju</t>
-  </si>
-  <si>
-    <t>lokesh</t>
-  </si>
-  <si>
-    <t>Poojamani</t>
-  </si>
-  <si>
-    <t>mahesh</t>
-  </si>
-  <si>
-    <t>Ramya</t>
-  </si>
-  <si>
-    <t>BHRPL6522E</t>
-  </si>
-  <si>
-    <t>bhrpl6522d</t>
-  </si>
-  <si>
-    <t>jdnkn3737r</t>
-  </si>
-  <si>
-    <t>hshsh2727y</t>
-  </si>
-  <si>
-    <t>hshsh2727h</t>
-  </si>
-  <si>
-    <t>hshsh5252f</t>
-  </si>
-  <si>
-    <t>BHYEJ2828E</t>
-  </si>
-  <si>
-    <t>HSHSH3535G</t>
-  </si>
-  <si>
-    <t>36DCRPS5473P1ZC</t>
-  </si>
-  <si>
-    <t>36DCRPS5473P1Ze</t>
-  </si>
-  <si>
-    <t>36kshdh2737nd24</t>
-  </si>
-  <si>
-    <t>sdvbksdjvskjvn</t>
-  </si>
-  <si>
-    <t>bchdvbsdvbk</t>
-  </si>
-  <si>
-    <t>hbdbvdhvbksdvk</t>
-  </si>
-  <si>
-    <t>KDVSIYDVBSDNYI</t>
-  </si>
-  <si>
-    <t>2026-27</t>
-  </si>
-  <si>
-    <t>Pending</t>
-  </si>
-  <si>
-    <t>Received</t>
-  </si>
-  <si>
-    <t>Completed</t>
-  </si>
-  <si>
-    <t>Not Filed</t>
-  </si>
-  <si>
-    <t>Filed</t>
-  </si>
-  <si>
-    <t>Lokesh</t>
   </si>
 </sst>
 </file>
@@ -465,7 +375,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
@@ -500,256 +410,6 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F2" t="s">
-        <v>34</v>
-      </c>
-      <c r="G2" t="s">
-        <v>37</v>
-      </c>
-      <c r="H2" t="s">
-        <v>37</v>
-      </c>
-      <c r="I2" t="s">
-        <v>39</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D3" t="s">
-        <v>33</v>
-      </c>
-      <c r="E3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G3" t="s">
-        <v>37</v>
-      </c>
-      <c r="H3" t="s">
-        <v>37</v>
-      </c>
-      <c r="I3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D4" t="s">
-        <v>33</v>
-      </c>
-      <c r="E4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F4" t="s">
-        <v>34</v>
-      </c>
-      <c r="G4" t="s">
-        <v>37</v>
-      </c>
-      <c r="H4" t="s">
-        <v>37</v>
-      </c>
-      <c r="I4" t="s">
-        <v>39</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D5" t="s">
-        <v>33</v>
-      </c>
-      <c r="E5" t="s">
-        <v>35</v>
-      </c>
-      <c r="F5" t="s">
-        <v>34</v>
-      </c>
-      <c r="G5" t="s">
-        <v>37</v>
-      </c>
-      <c r="H5" t="s">
-        <v>37</v>
-      </c>
-      <c r="I5" t="s">
-        <v>39</v>
-      </c>
-      <c r="J5">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" t="s">
-        <v>30</v>
-      </c>
-      <c r="D6" t="s">
-        <v>33</v>
-      </c>
-      <c r="E6" t="s">
-        <v>34</v>
-      </c>
-      <c r="F6" t="s">
-        <v>34</v>
-      </c>
-      <c r="G6" t="s">
-        <v>37</v>
-      </c>
-      <c r="H6" t="s">
-        <v>37</v>
-      </c>
-      <c r="I6" t="s">
-        <v>39</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" t="s">
-        <v>31</v>
-      </c>
-      <c r="D7" t="s">
-        <v>33</v>
-      </c>
-      <c r="E7" t="s">
-        <v>35</v>
-      </c>
-      <c r="F7" t="s">
-        <v>36</v>
-      </c>
-      <c r="G7" t="s">
-        <v>38</v>
-      </c>
-      <c r="H7" t="s">
-        <v>38</v>
-      </c>
-      <c r="I7" t="s">
-        <v>14</v>
-      </c>
-      <c r="J7">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" t="s">
-        <v>32</v>
-      </c>
-      <c r="D8" t="s">
-        <v>33</v>
-      </c>
-      <c r="E8" t="s">
-        <v>34</v>
-      </c>
-      <c r="F8" t="s">
-        <v>34</v>
-      </c>
-      <c r="G8" t="s">
-        <v>37</v>
-      </c>
-      <c r="H8" t="s">
-        <v>37</v>
-      </c>
-      <c r="I8" t="s">
-        <v>14</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" t="s">
-        <v>17</v>
-      </c>
-      <c r="B9" t="s">
-        <v>25</v>
-      </c>
-      <c r="D9" t="s">
-        <v>33</v>
-      </c>
-      <c r="E9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F9" t="s">
-        <v>34</v>
-      </c>
-      <c r="G9" t="s">
-        <v>37</v>
-      </c>
-      <c r="H9" t="s">
-        <v>37</v>
-      </c>
-      <c r="J9">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
